--- a/Shared/DocumentsValidationData/Passing/8XXX_IOyyyy_R0.0_EmergencyIoListValidationTemplate.xlsx
+++ b/Shared/DocumentsValidationData/Passing/8XXX_IOyyyy_R0.0_EmergencyIoListValidationTemplate.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5D438BD-CB21-474D-82D8-A230375FD213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEAD1951-1AA4-4429-BD6B-DA7D217ACF47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17790" activeTab="1" xr2:uid="{9FADC895-0395-4F4D-A5BB-C71DE81AA975}"/>
   </bookViews>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2351" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2295" uniqueCount="487">
   <si>
     <t>0</t>
   </si>
@@ -1517,6 +1517,24 @@
   </si>
   <si>
     <t>-S67008</t>
+  </si>
+  <si>
+    <t>+EmergencyAreas_1</t>
+  </si>
+  <si>
+    <t>021</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>-X40001</t>
+  </si>
+  <si>
+    <t>016</t>
   </si>
 </sst>
 </file>
@@ -1860,7 +1878,7 @@
     <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyFont="1"/>
@@ -2053,6 +2071,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="ColStyle10 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -2065,28 +2086,7 @@
     <cellStyle name="Normale 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
     <cellStyle name="Valore valido 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
   </cellStyles>
-  <dxfs count="53">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="51">
     <dxf>
       <fill>
         <patternFill>
@@ -2224,27 +2224,6 @@
         </top>
         <bottom style="thin">
           <color indexed="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
         </bottom>
       </border>
     </dxf>
@@ -4359,8 +4338,8 @@
       <c r="AE5" s="42" t="s">
         <v>350</v>
       </c>
-      <c r="AF5" s="51" t="s">
-        <v>351</v>
+      <c r="AF5" s="56" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
@@ -4442,8 +4421,8 @@
       <c r="AE6" s="42" t="s">
         <v>350</v>
       </c>
-      <c r="AF6" s="51" t="s">
-        <v>353</v>
+      <c r="AF6" s="56" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
@@ -4587,8 +4566,8 @@
       <c r="AE8" s="42" t="s">
         <v>355</v>
       </c>
-      <c r="AF8" s="51" t="s">
-        <v>351</v>
+      <c r="AF8" s="56" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
@@ -7062,11 +7041,11 @@
       <c r="AD41" s="51" t="s">
         <v>349</v>
       </c>
-      <c r="AE41" s="42" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF41" s="51" t="s">
-        <v>30</v>
+      <c r="AE41" s="59" t="s">
+        <v>482</v>
+      </c>
+      <c r="AF41" s="56" t="s">
+        <v>353</v>
       </c>
       <c r="AG41" t="s">
         <v>440</v>
@@ -7138,11 +7117,11 @@
       <c r="AD42" s="51" t="s">
         <v>349</v>
       </c>
-      <c r="AE42" s="42" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF42" s="51" t="s">
-        <v>30</v>
+      <c r="AE42" s="59" t="s">
+        <v>482</v>
+      </c>
+      <c r="AF42" s="56" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.25">
@@ -7211,11 +7190,11 @@
       <c r="AD43" s="51" t="s">
         <v>349</v>
       </c>
-      <c r="AE43" s="42" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF43" s="51" t="s">
-        <v>30</v>
+      <c r="AE43" s="59" t="s">
+        <v>482</v>
+      </c>
+      <c r="AF43" s="56" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.25">
@@ -8393,7 +8372,9 @@
       <c r="P60" s="28" t="s">
         <v>199</v>
       </c>
-      <c r="Q60" s="21"/>
+      <c r="Q60" s="70" t="s">
+        <v>485</v>
+      </c>
       <c r="R60" s="21"/>
       <c r="S60" s="20" t="s">
         <v>278</v>
@@ -8417,14 +8398,14 @@
         <f ca="1"/>
         <v>???</v>
       </c>
-      <c r="AD60" s="51" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE60" s="42" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF60" s="51" t="s">
-        <v>30</v>
+      <c r="AD60" s="56" t="s">
+        <v>349</v>
+      </c>
+      <c r="AE60" s="59" t="s">
+        <v>486</v>
+      </c>
+      <c r="AF60" s="56" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="61" spans="1:32" x14ac:dyDescent="0.25">
@@ -8656,8 +8637,8 @@
         <f ca="1"/>
         <v>RES</v>
       </c>
-      <c r="AD63" s="51" t="s">
-        <v>30</v>
+      <c r="AD63" s="56" t="s">
+        <v>352</v>
       </c>
       <c r="AE63" s="42" t="s">
         <v>30</v>
@@ -8705,7 +8686,9 @@
       <c r="P64" s="29" t="s">
         <v>199</v>
       </c>
-      <c r="Q64" s="29"/>
+      <c r="Q64" s="70" t="s">
+        <v>485</v>
+      </c>
       <c r="R64" s="22"/>
       <c r="S64" s="22" t="s">
         <v>278</v>
@@ -8818,8 +8801,8 @@
       <c r="AE65" s="42" t="s">
         <v>380</v>
       </c>
-      <c r="AF65" s="51" t="s">
-        <v>365</v>
+      <c r="AF65" s="56" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="66" spans="1:32" x14ac:dyDescent="0.25">
@@ -12919,8 +12902,8 @@
       <c r="AE122" s="42" t="s">
         <v>403</v>
       </c>
-      <c r="AF122" s="51" t="s">
-        <v>353</v>
+      <c r="AF122" s="56" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="123" spans="1:32" x14ac:dyDescent="0.25">
@@ -14122,264 +14105,254 @@
   <dataConsolidate/>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="A82:A121 K100:P102 K104:P115 K118:P119">
-    <cfRule type="expression" dxfId="52" priority="250" stopIfTrue="1">
+    <cfRule type="expression" dxfId="50" priority="250" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A122:P122 U122 X122:AC122">
-    <cfRule type="expression" dxfId="51" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="49" priority="15" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:W6 E8:T8 V8:W8">
-    <cfRule type="expression" dxfId="50" priority="1137" stopIfTrue="1">
+    <cfRule type="expression" dxfId="48" priority="1137" stopIfTrue="1">
       <formula>$X3="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:X2">
-    <cfRule type="expression" dxfId="49" priority="1304" stopIfTrue="1">
+    <cfRule type="expression" dxfId="47" priority="1304" stopIfTrue="1">
       <formula>$Y1="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A123:AC138">
-    <cfRule type="expression" dxfId="48" priority="16" stopIfTrue="1">
+    <cfRule type="expression" dxfId="46" priority="16" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="expression" dxfId="47" priority="578" stopIfTrue="1">
+    <cfRule type="expression" dxfId="45" priority="578" stopIfTrue="1">
       <formula>$X8="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B65">
-    <cfRule type="expression" dxfId="46" priority="535" stopIfTrue="1">
+    <cfRule type="expression" dxfId="44" priority="535" stopIfTrue="1">
       <formula>$X65="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7:AC7">
-    <cfRule type="expression" dxfId="45" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="43" priority="11" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E65">
-    <cfRule type="expression" dxfId="44" priority="536" stopIfTrue="1">
+    <cfRule type="expression" dxfId="42" priority="536" stopIfTrue="1">
       <formula>$X65="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E65:H65">
-    <cfRule type="expression" dxfId="43" priority="537" stopIfTrue="1">
+    <cfRule type="expression" dxfId="41" priority="537" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8:Q8 U8 X8:AC8">
-    <cfRule type="expression" dxfId="42" priority="1246" stopIfTrue="1">
+    <cfRule type="expression" dxfId="40" priority="1246" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G121">
-    <cfRule type="duplicateValues" dxfId="41" priority="1364"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="1364"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G122:G138">
-    <cfRule type="duplicateValues" dxfId="40" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I65 V65:W65">
-    <cfRule type="expression" dxfId="39" priority="797" stopIfTrue="1">
+    <cfRule type="expression" dxfId="37" priority="797" stopIfTrue="1">
       <formula>$X65="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I65:Q65">
-    <cfRule type="expression" dxfId="38" priority="390" stopIfTrue="1">
+    <cfRule type="expression" dxfId="36" priority="390" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J9:J56 D9:I64 K10:N28 O10:O40 P17:AC56 D66:I121">
-    <cfRule type="expression" dxfId="37" priority="844" stopIfTrue="1">
+    <cfRule type="expression" dxfId="35" priority="844" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J66:J97">
-    <cfRule type="expression" dxfId="36" priority="531" stopIfTrue="1">
+    <cfRule type="expression" dxfId="34" priority="531" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K29 M29:N29 K30:N32 M33:N37 K38:N40">
-    <cfRule type="expression" dxfId="35" priority="1122" stopIfTrue="1">
+    <cfRule type="expression" dxfId="33" priority="1122" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K33:K37">
-    <cfRule type="expression" dxfId="34" priority="562" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="562" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K113">
-    <cfRule type="expression" dxfId="33" priority="378" stopIfTrue="1">
-      <formula>#REF!="PA"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M64:N64">
-    <cfRule type="expression" dxfId="32" priority="1101" stopIfTrue="1">
+    <cfRule type="expression" dxfId="31" priority="378" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K41:O58 A41:A64 P57:X58 K59:Q59 S59:X59 M60:P60 S60:T60 V60:X60 K61:X62">
-    <cfRule type="expression" dxfId="31" priority="1021" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="1021" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K66:P98">
-    <cfRule type="expression" dxfId="30" priority="384" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="384" stopIfTrue="1">
+      <formula>#REF!="PA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K63:Q63 S63:X63">
+    <cfRule type="expression" dxfId="28" priority="1" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K116:Q117 K120:Q121">
-    <cfRule type="expression" dxfId="29" priority="380" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="380" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9:AC9 Q10:AC13 Q14:V14 X14:AC14 Q15:AC16">
-    <cfRule type="expression" dxfId="28" priority="1116" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="1116" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K99:AC99">
-    <cfRule type="expression" dxfId="27" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="20" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K103:AC103">
-    <cfRule type="expression" dxfId="26" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="19" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L33:L36">
-    <cfRule type="expression" dxfId="25" priority="561" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="561" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L108">
-    <cfRule type="expression" dxfId="24" priority="379" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="379" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L112:L113">
-    <cfRule type="expression" dxfId="23" priority="377" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="377" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O64:Q64">
-    <cfRule type="expression" dxfId="22" priority="849" stopIfTrue="1">
+  <conditionalFormatting sqref="M64:P64 R64:X64">
+    <cfRule type="expression" dxfId="20" priority="849" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P10:P16">
-    <cfRule type="expression" dxfId="21" priority="1099" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="1099" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q75:Q97">
-    <cfRule type="expression" dxfId="20" priority="373" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="373" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q114">
-    <cfRule type="expression" dxfId="19" priority="383" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="383" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q118">
-    <cfRule type="expression" dxfId="18" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="2" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q122:T122">
-    <cfRule type="expression" dxfId="17" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="17" stopIfTrue="1">
       <formula>$X122="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q66:X74">
-    <cfRule type="expression" dxfId="16" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="4" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q104:X105">
-    <cfRule type="expression" dxfId="15" priority="523" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="523" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R106:S113 U106:W113">
-    <cfRule type="expression" dxfId="14" priority="775" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="775" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R65:T65">
-    <cfRule type="expression" dxfId="13" priority="1195" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="1195" stopIfTrue="1">
       <formula>$X65="PA"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R64:X64">
-    <cfRule type="expression" dxfId="12" priority="1134" stopIfTrue="1">
-      <formula>#REF!="PA"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="R75:X79 R80:S83 U80:X83 R84:X98 R100:AC102">
-    <cfRule type="expression" dxfId="11" priority="524" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="524" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R114:AC121">
-    <cfRule type="expression" dxfId="10" priority="1123" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="1123" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T80:T81">
-    <cfRule type="expression" dxfId="9" priority="374" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="374" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U65 X65:AC65">
-    <cfRule type="expression" dxfId="8" priority="1196" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="1196" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V122:W122">
-    <cfRule type="expression" dxfId="7" priority="18" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="18" stopIfTrue="1">
       <formula>$X122="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X3:X6">
-    <cfRule type="expression" dxfId="6" priority="1164" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="1164" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y1:AC2">
-    <cfRule type="expression" dxfId="5" priority="1326" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="1326" stopIfTrue="1">
       <formula>$X1="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y3:AC6">
-    <cfRule type="expression" dxfId="4" priority="1167" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="1167" stopIfTrue="1">
       <formula>$X3="PA"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y66:AC98 Y104:AC107 X106:X107 X108:AC113 Y57:AC64">
-    <cfRule type="expression" dxfId="3" priority="1243" stopIfTrue="1">
+  <conditionalFormatting sqref="Y57:AC64 Y66:AC98 Y104:AC107 X106:X107 X108:AC113">
+    <cfRule type="expression" dxfId="2" priority="1243" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD1:AD121 AD139:AD144">
-    <cfRule type="expression" dxfId="2" priority="1366">
+    <cfRule type="expression" dxfId="1" priority="1366">
       <formula>IF($AD1&lt;&gt;"", SUM(--(($AC1 &amp;"-" &amp;$AD1)=(_xlfn._TRO_TRAILING($AC$1:$AC$9236) &amp;"-" &amp;_xlfn._TRO_TRAILING($AD$1:$AD$9236))))&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD122:AD138">
-    <cfRule type="expression" dxfId="1" priority="13">
+    <cfRule type="expression" dxfId="0" priority="13">
       <formula>IF($AD122&lt;&gt;"", SUM(--(($AC122 &amp;"-" &amp;$AD122)=(_xlfn._TRO_TRAILING($AC$1:$AC$10004) &amp;"-" &amp;_xlfn._TRO_TRAILING($AD$1:$AD$10004))))&gt;1)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K63:Q63 S63:X63">
-    <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
-      <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14396,7 +14369,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FFADF65-5563-4E8A-AE6F-6C40CA30FD51}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
@@ -14439,7 +14412,7 @@
         <v>0</v>
       </c>
       <c r="B2" cm="1">
-        <f t="array" ref="B2:B15">_xlfn._TRO_TRAILING(A2:A992)</f>
+        <f t="array" ref="B2:B16">_xlfn._TRO_TRAILING(A2:A992)</f>
         <v>0</v>
       </c>
       <c r="C2" s="53" t="s">
@@ -14449,14 +14422,14 @@
         <v>198</v>
       </c>
       <c r="E2" t="str" cm="1">
-        <f t="array" ref="E2:E15">"=S1" &amp;_xlfn._TRO_TRAILING(D2:D93)</f>
+        <f t="array" ref="E2:E16">"=S1" &amp;_xlfn._TRO_TRAILING(D2:D93)</f>
         <v>=S1+MC1.CC1</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="H2" cm="1">
-        <f t="array" ref="H2:H15">_xlfn.LET(
+        <f t="array" ref="H2:H16">_xlfn.LET(
     _xlpm.cab_indexes,_xlfn._TRO_TRAILING( DiagnosisBlocks!A2:A999),
     _xlpm.cab_indexes_lookup_col, _xlfn.VSTACK('NET SAFETY 50'!AE:AE),
     IFERROR(
@@ -14674,7 +14647,7 @@
         <v>2</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -14767,6 +14740,29 @@
       </c>
       <c r="H15">
         <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>21</v>
+      </c>
+      <c r="B16">
+        <v>21</v>
+      </c>
+      <c r="C16" s="53" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="53" t="s">
+        <v>481</v>
+      </c>
+      <c r="E16" t="str">
+        <v>=S1+EmergencyAreas_1</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="H16">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Shared/DocumentsValidationData/Passing/8XXX_IOyyyy_R0.0_EmergencyIoListValidationTemplate.xlsx
+++ b/Shared/DocumentsValidationData/Passing/8XXX_IOyyyy_R0.0_EmergencyIoListValidationTemplate.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEAD1951-1AA4-4429-BD6B-DA7D217ACF47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F4F5245-47AB-4406-A987-D66A9DCAC8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17790" activeTab="1" xr2:uid="{9FADC895-0395-4F4D-A5BB-C71DE81AA975}"/>
   </bookViews>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2295" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2292" uniqueCount="487">
   <si>
     <t>0</t>
   </si>
@@ -12686,9 +12686,7 @@
       <c r="AA119" s="55">
         <v>0</v>
       </c>
-      <c r="AB119" s="45" t="s">
-        <v>327</v>
-      </c>
+      <c r="AB119" s="45"/>
       <c r="AC119" s="49" t="str">
         <f ca="1"/>
         <v/>
@@ -12749,9 +12747,7 @@
       <c r="AA120" s="55">
         <v>0</v>
       </c>
-      <c r="AB120" s="45" t="s">
-        <v>330</v>
-      </c>
+      <c r="AB120" s="45"/>
       <c r="AC120" s="49" t="str">
         <f ca="1"/>
         <v/>
@@ -12812,9 +12808,7 @@
       <c r="AA121" s="55">
         <v>0</v>
       </c>
-      <c r="AB121" s="45" t="s">
-        <v>330</v>
-      </c>
+      <c r="AB121" s="45"/>
       <c r="AC121" s="49" t="str">
         <f ca="1"/>
         <v/>

--- a/Shared/DocumentsValidationData/Passing/8XXX_IOyyyy_R0.0_EmergencyIoListValidationTemplate.xlsx
+++ b/Shared/DocumentsValidationData/Passing/8XXX_IOyyyy_R0.0_EmergencyIoListValidationTemplate.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F4F5245-47AB-4406-A987-D66A9DCAC8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74F30B35-8E30-4920-9474-D95799298B4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17790" activeTab="1" xr2:uid="{9FADC895-0395-4F4D-A5BB-C71DE81AA975}"/>
   </bookViews>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2292" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2293" uniqueCount="487">
   <si>
     <t>0</t>
   </si>
@@ -4483,9 +4483,6 @@
       <c r="AF7" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="AG7" t="s">
-        <v>440</v>
-      </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
@@ -8722,7 +8719,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="65" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A65" s="18" t="s">
         <v>238</v>
       </c>
@@ -8805,7 +8802,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="66" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A66" s="35" t="s">
         <v>35</v>
       </c>
@@ -8879,8 +8876,11 @@
       <c r="AF66" s="51" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="67" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG66" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="67" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A67" s="35" t="s">
         <v>35</v>
       </c>
@@ -8955,7 +8955,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="68" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A68" s="35" t="s">
         <v>35</v>
       </c>
@@ -9030,7 +9030,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="69" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A69" s="35" t="s">
         <v>35</v>
       </c>
@@ -9105,7 +9105,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="70" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A70" s="35" t="s">
         <v>35</v>
       </c>
@@ -9174,7 +9174,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="71" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A71" s="35" t="s">
         <v>35</v>
       </c>
@@ -9243,7 +9243,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A72" s="35" t="s">
         <v>35</v>
       </c>
@@ -9312,7 +9312,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="73" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A73" s="35" t="s">
         <v>35</v>
       </c>
@@ -9381,7 +9381,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="74" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A74" s="35" t="s">
         <v>35</v>
       </c>
@@ -9458,7 +9458,7 @@
       <c r="AE74" s="19"/>
       <c r="AF74" s="19"/>
     </row>
-    <row r="75" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A75" s="35" t="s">
         <v>35</v>
       </c>
@@ -9535,7 +9535,7 @@
       <c r="AE75" s="19"/>
       <c r="AF75" s="19"/>
     </row>
-    <row r="76" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A76" s="35" t="s">
         <v>35</v>
       </c>
@@ -9604,7 +9604,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="77" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A77" s="35" t="s">
         <v>35</v>
       </c>
@@ -9673,7 +9673,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="78" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A78" s="35" t="s">
         <v>35</v>
       </c>
@@ -9742,7 +9742,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="79" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A79" s="35" t="s">
         <v>35</v>
       </c>
@@ -9811,7 +9811,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="80" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A80" s="35" t="s">
         <v>35</v>
       </c>
@@ -12188,7 +12188,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="113" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A113" s="22" t="s">
         <v>53</v>
       </c>
@@ -12261,7 +12261,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="114" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A114" s="20" t="s">
         <v>309</v>
       </c>
@@ -12335,8 +12335,11 @@
       <c r="AF114" s="51" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="115" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG114" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="115" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A115" s="20" t="s">
         <v>309</v>
       </c>
@@ -12411,7 +12414,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="116" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A116" s="20" t="s">
         <v>309</v>
       </c>
@@ -12486,7 +12489,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="117" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A117" s="22" t="s">
         <v>309</v>
       </c>
@@ -12561,7 +12564,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="118" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A118" s="20" t="s">
         <v>309</v>
       </c>
@@ -12634,7 +12637,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="119" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A119" s="20" t="s">
         <v>309</v>
       </c>
@@ -12695,7 +12698,7 @@
       <c r="AE119" s="42"/>
       <c r="AF119" s="51"/>
     </row>
-    <row r="120" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A120" s="20" t="s">
         <v>309</v>
       </c>
@@ -12756,7 +12759,7 @@
       <c r="AE120" s="42"/>
       <c r="AF120" s="51"/>
     </row>
-    <row r="121" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A121" s="22" t="s">
         <v>309</v>
       </c>
@@ -12817,7 +12820,7 @@
       <c r="AE121" s="42"/>
       <c r="AF121" s="51"/>
     </row>
-    <row r="122" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A122" s="18" t="s">
         <v>394</v>
       </c>
@@ -12900,7 +12903,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="123" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A123" s="20" t="s">
         <v>404</v>
       </c>
@@ -12963,7 +12966,7 @@
       <c r="AE123" s="42"/>
       <c r="AF123" s="51"/>
     </row>
-    <row r="124" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A124" s="20" t="s">
         <v>404</v>
       </c>
@@ -13026,7 +13029,7 @@
       <c r="AE124" s="42"/>
       <c r="AF124" s="51"/>
     </row>
-    <row r="125" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A125" s="20" t="s">
         <v>404</v>
       </c>
@@ -13089,7 +13092,7 @@
       <c r="AE125" s="42"/>
       <c r="AF125" s="51"/>
     </row>
-    <row r="126" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A126" s="20" t="s">
         <v>404</v>
       </c>
@@ -13152,7 +13155,7 @@
       <c r="AE126" s="42"/>
       <c r="AF126" s="51"/>
     </row>
-    <row r="127" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A127" s="20" t="s">
         <v>404</v>
       </c>
@@ -13215,7 +13218,7 @@
       <c r="AE127" s="42"/>
       <c r="AF127" s="51"/>
     </row>
-    <row r="128" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A128" s="20" t="s">
         <v>404</v>
       </c>

--- a/Shared/DocumentsValidationData/Passing/8XXX_IOyyyy_R0.0_EmergencyIoListValidationTemplate.xlsx
+++ b/Shared/DocumentsValidationData/Passing/8XXX_IOyyyy_R0.0_EmergencyIoListValidationTemplate.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E3017A0-C184-4A5C-8EBD-8F17DFD4E5EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22C05FCF-8821-4FE3-AF4C-490C776B421B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17790" activeTab="2" xr2:uid="{9FADC895-0395-4F4D-A5BB-C71DE81AA975}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3522" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3518" uniqueCount="538">
   <si>
     <t>0</t>
   </si>
@@ -1661,6 +1661,9 @@
   </si>
   <si>
     <t>=S2</t>
+  </si>
+  <si>
+    <t>EMERGENCY AREA 4</t>
   </si>
 </sst>
 </file>
@@ -2193,12 +2196,6 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2214,6 +2211,12 @@
     <xf numFmtId="49" fontId="3" fillId="7" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="ColStyle10 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -2226,672 +2229,7 @@
     <cellStyle name="Normale 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
     <cellStyle name="Valore valido 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
   </cellStyles>
-  <dxfs count="132">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color indexed="0"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color indexed="0"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color indexed="0"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color indexed="0"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color indexed="0"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color indexed="0"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color indexed="0"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color indexed="0"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="100">
     <dxf>
       <fill>
         <patternFill>
@@ -2903,16 +2241,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF8B8B"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3647,6 +2975,16 @@
           <color indexed="0"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -5310,26 +4648,26 @@
       <c r="B1" s="1"/>
     </row>
     <row r="2" spans="2:6" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="73" t="s">
         <v>330</v>
       </c>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
     </row>
     <row r="3" spans="2:6" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="69" t="s">
+      <c r="B3" s="74" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
     </row>
     <row r="4" spans="2:6" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="69"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
+      <c r="B4" s="74"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
     </row>
     <row r="5" spans="2:6" s="2" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="1"/>
@@ -14137,253 +13475,253 @@
   <dataConsolidate/>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="A82:A121 K100:P102 K104:P115 K118:P119">
-    <cfRule type="expression" dxfId="131" priority="250" stopIfTrue="1">
+    <cfRule type="expression" dxfId="99" priority="250" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A122:P122 U122 X122:AC122">
-    <cfRule type="expression" dxfId="130" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="98" priority="15" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:W6 E8:T8 V8:W8">
-    <cfRule type="expression" dxfId="129" priority="1137" stopIfTrue="1">
+    <cfRule type="expression" dxfId="97" priority="1137" stopIfTrue="1">
       <formula>$X3="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:X2">
-    <cfRule type="expression" dxfId="128" priority="1304" stopIfTrue="1">
+    <cfRule type="expression" dxfId="96" priority="1304" stopIfTrue="1">
       <formula>$Y1="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A123:AC138">
-    <cfRule type="expression" dxfId="127" priority="16" stopIfTrue="1">
+    <cfRule type="expression" dxfId="95" priority="16" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="expression" dxfId="126" priority="578" stopIfTrue="1">
+    <cfRule type="expression" dxfId="94" priority="578" stopIfTrue="1">
       <formula>$X8="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B65">
-    <cfRule type="expression" dxfId="125" priority="535" stopIfTrue="1">
+    <cfRule type="expression" dxfId="93" priority="535" stopIfTrue="1">
       <formula>$X65="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7:AC7">
-    <cfRule type="expression" dxfId="124" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="92" priority="11" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E65">
-    <cfRule type="expression" dxfId="123" priority="536" stopIfTrue="1">
+    <cfRule type="expression" dxfId="91" priority="536" stopIfTrue="1">
       <formula>$X65="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E65:H65">
-    <cfRule type="expression" dxfId="122" priority="537" stopIfTrue="1">
+    <cfRule type="expression" dxfId="90" priority="537" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8:Q8 U8 X8:AC8">
-    <cfRule type="expression" dxfId="121" priority="1246" stopIfTrue="1">
+    <cfRule type="expression" dxfId="89" priority="1246" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G121">
-    <cfRule type="duplicateValues" dxfId="120" priority="1364"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="1364"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G122:G138">
-    <cfRule type="duplicateValues" dxfId="119" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I65 V65:W65">
-    <cfRule type="expression" dxfId="118" priority="797" stopIfTrue="1">
+    <cfRule type="expression" dxfId="86" priority="797" stopIfTrue="1">
       <formula>$X65="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I65:Q65">
-    <cfRule type="expression" dxfId="117" priority="390" stopIfTrue="1">
+    <cfRule type="expression" dxfId="85" priority="390" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J9:J56 D9:I64 K10:N28 O10:O40 P17:AC56 D66:I121">
-    <cfRule type="expression" dxfId="116" priority="844" stopIfTrue="1">
+    <cfRule type="expression" dxfId="84" priority="844" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J66:J97">
-    <cfRule type="expression" dxfId="115" priority="531" stopIfTrue="1">
+    <cfRule type="expression" dxfId="83" priority="531" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K29 M29:N29 K30:N32 M33:N37 K38:N40">
-    <cfRule type="expression" dxfId="114" priority="1122" stopIfTrue="1">
+    <cfRule type="expression" dxfId="82" priority="1122" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K33:K37">
-    <cfRule type="expression" dxfId="113" priority="562" stopIfTrue="1">
+    <cfRule type="expression" dxfId="81" priority="562" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K113">
-    <cfRule type="expression" dxfId="112" priority="378" stopIfTrue="1">
+    <cfRule type="expression" dxfId="80" priority="378" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K41:O58 A41:A64 P57:X58 K59:Q59 S59:X59 M60:P60 S60:T60 V60:X60 K61:X62">
-    <cfRule type="expression" dxfId="111" priority="1021" stopIfTrue="1">
+    <cfRule type="expression" dxfId="79" priority="1021" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K66:P98">
-    <cfRule type="expression" dxfId="110" priority="384" stopIfTrue="1">
+    <cfRule type="expression" dxfId="78" priority="384" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K63:Q63 S63:X63">
-    <cfRule type="expression" dxfId="109" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="77" priority="1" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K116:Q117 K120:Q121">
-    <cfRule type="expression" dxfId="108" priority="380" stopIfTrue="1">
+    <cfRule type="expression" dxfId="76" priority="380" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9:AC9 Q10:AC13 Q14:V14 X14:AC14 Q15:AC16">
-    <cfRule type="expression" dxfId="107" priority="1116" stopIfTrue="1">
+    <cfRule type="expression" dxfId="75" priority="1116" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K99:AC99">
-    <cfRule type="expression" dxfId="106" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="74" priority="20" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K103:AC103">
-    <cfRule type="expression" dxfId="105" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="73" priority="19" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L33:L36">
-    <cfRule type="expression" dxfId="104" priority="561" stopIfTrue="1">
+    <cfRule type="expression" dxfId="72" priority="561" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L108">
-    <cfRule type="expression" dxfId="103" priority="379" stopIfTrue="1">
+    <cfRule type="expression" dxfId="71" priority="379" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L112:L113">
-    <cfRule type="expression" dxfId="102" priority="377" stopIfTrue="1">
+    <cfRule type="expression" dxfId="70" priority="377" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M64:P64 R64:X64">
-    <cfRule type="expression" dxfId="101" priority="849" stopIfTrue="1">
+    <cfRule type="expression" dxfId="69" priority="849" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P10:P16">
-    <cfRule type="expression" dxfId="100" priority="1099" stopIfTrue="1">
+    <cfRule type="expression" dxfId="68" priority="1099" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q75:Q97">
-    <cfRule type="expression" dxfId="99" priority="373" stopIfTrue="1">
+    <cfRule type="expression" dxfId="67" priority="373" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q114">
-    <cfRule type="expression" dxfId="98" priority="383" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="383" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q118">
-    <cfRule type="expression" dxfId="97" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="65" priority="2" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q122:T122">
-    <cfRule type="expression" dxfId="96" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="64" priority="17" stopIfTrue="1">
       <formula>$X122="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q66:X74">
-    <cfRule type="expression" dxfId="95" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="63" priority="4" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q104:X105">
-    <cfRule type="expression" dxfId="94" priority="523" stopIfTrue="1">
+    <cfRule type="expression" dxfId="62" priority="523" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R106:S113 U106:W113">
-    <cfRule type="expression" dxfId="93" priority="775" stopIfTrue="1">
+    <cfRule type="expression" dxfId="61" priority="775" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R65:T65">
-    <cfRule type="expression" dxfId="92" priority="1195" stopIfTrue="1">
+    <cfRule type="expression" dxfId="60" priority="1195" stopIfTrue="1">
       <formula>$X65="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R75:X79 R80:S83 U80:X83 R84:X98 R100:AC102">
-    <cfRule type="expression" dxfId="91" priority="524" stopIfTrue="1">
+    <cfRule type="expression" dxfId="59" priority="524" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R114:AC121">
-    <cfRule type="expression" dxfId="90" priority="1123" stopIfTrue="1">
+    <cfRule type="expression" dxfId="58" priority="1123" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T80:T81">
-    <cfRule type="expression" dxfId="89" priority="374" stopIfTrue="1">
+    <cfRule type="expression" dxfId="57" priority="374" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U65 X65:AC65">
-    <cfRule type="expression" dxfId="88" priority="1196" stopIfTrue="1">
+    <cfRule type="expression" dxfId="56" priority="1196" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V122:W122">
-    <cfRule type="expression" dxfId="87" priority="18" stopIfTrue="1">
+    <cfRule type="expression" dxfId="55" priority="18" stopIfTrue="1">
       <formula>$X122="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X3:X6">
-    <cfRule type="expression" dxfId="86" priority="1164" stopIfTrue="1">
+    <cfRule type="expression" dxfId="54" priority="1164" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y1:AC2">
-    <cfRule type="expression" dxfId="85" priority="1326" stopIfTrue="1">
+    <cfRule type="expression" dxfId="53" priority="1326" stopIfTrue="1">
       <formula>$X1="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y3:AC6">
-    <cfRule type="expression" dxfId="84" priority="1167" stopIfTrue="1">
+    <cfRule type="expression" dxfId="52" priority="1167" stopIfTrue="1">
       <formula>$X3="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y57:AC64 Y66:AC98 Y104:AC107 X106:X107 X108:AC113">
-    <cfRule type="expression" dxfId="83" priority="1243" stopIfTrue="1">
+    <cfRule type="expression" dxfId="51" priority="1243" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD1:AD121 AD139:AD144">
-    <cfRule type="expression" dxfId="82" priority="1366">
+    <cfRule type="expression" dxfId="50" priority="1366">
       <formula>IF($AD1&lt;&gt;"", SUM(--(($AC1 &amp;"-" &amp;$AD1)=(_xlfn._TRO_TRAILING($AC$1:$AC$9236) &amp;"-" &amp;_xlfn._TRO_TRAILING($AD$1:$AD$9236))))&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD122:AD138">
-    <cfRule type="expression" dxfId="81" priority="13">
+    <cfRule type="expression" dxfId="49" priority="13">
       <formula>IF($AD122&lt;&gt;"", SUM(--(($AC122 &amp;"-" &amp;$AD122)=(_xlfn._TRO_TRAILING($AC$1:$AC$10004) &amp;"-" &amp;_xlfn._TRO_TRAILING($AD$1:$AD$10004))))&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14608,10 +13946,10 @@
         <v>206</v>
       </c>
       <c r="N3" s="18"/>
-      <c r="O3" s="74" t="s">
+      <c r="O3" s="72" t="s">
         <v>536</v>
       </c>
-      <c r="P3" s="70" t="s">
+      <c r="P3" s="68" t="s">
         <v>527</v>
       </c>
       <c r="Q3" s="30" t="s">
@@ -14678,10 +14016,10 @@
         <v>206</v>
       </c>
       <c r="N4" s="18"/>
-      <c r="O4" s="74" t="s">
+      <c r="O4" s="72" t="s">
         <v>536</v>
       </c>
-      <c r="P4" s="70" t="s">
+      <c r="P4" s="68" t="s">
         <v>527</v>
       </c>
       <c r="Q4" s="30" t="s">
@@ -14748,10 +14086,10 @@
         <v>66</v>
       </c>
       <c r="N5" s="18"/>
-      <c r="O5" s="74" t="s">
+      <c r="O5" s="72" t="s">
         <v>536</v>
       </c>
-      <c r="P5" s="70" t="s">
+      <c r="P5" s="68" t="s">
         <v>527</v>
       </c>
       <c r="Q5" s="30" t="s">
@@ -14818,10 +14156,10 @@
       <c r="L6" s="32"/>
       <c r="M6" s="32"/>
       <c r="N6" s="32"/>
-      <c r="O6" s="71" t="s">
+      <c r="O6" s="69" t="s">
         <v>536</v>
       </c>
-      <c r="P6" s="71" t="s">
+      <c r="P6" s="69" t="s">
         <v>529</v>
       </c>
       <c r="Q6" s="33" t="s">
@@ -14886,10 +14224,10 @@
       <c r="L7" s="20"/>
       <c r="M7" s="20"/>
       <c r="N7" s="20"/>
-      <c r="O7" s="72" t="s">
+      <c r="O7" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P7" s="72" t="s">
+      <c r="P7" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q7" s="20"/>
@@ -14945,10 +14283,10 @@
       <c r="L8" s="20"/>
       <c r="M8" s="20"/>
       <c r="N8" s="20"/>
-      <c r="O8" s="72" t="s">
+      <c r="O8" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P8" s="72" t="s">
+      <c r="P8" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q8" s="20"/>
@@ -15001,10 +14339,10 @@
       <c r="L9" s="20"/>
       <c r="M9" s="20"/>
       <c r="N9" s="20"/>
-      <c r="O9" s="72" t="s">
+      <c r="O9" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P9" s="72" t="s">
+      <c r="P9" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q9" s="20"/>
@@ -15057,10 +14395,10 @@
       <c r="L10" s="20"/>
       <c r="M10" s="20"/>
       <c r="N10" s="20"/>
-      <c r="O10" s="72" t="s">
+      <c r="O10" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P10" s="72" t="s">
+      <c r="P10" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q10" s="20"/>
@@ -15113,10 +14451,10 @@
       <c r="L11" s="20"/>
       <c r="M11" s="20"/>
       <c r="N11" s="20"/>
-      <c r="O11" s="72" t="s">
+      <c r="O11" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P11" s="72" t="s">
+      <c r="P11" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q11" s="20"/>
@@ -15169,10 +14507,10 @@
       <c r="L12" s="20"/>
       <c r="M12" s="20"/>
       <c r="N12" s="20"/>
-      <c r="O12" s="72" t="s">
+      <c r="O12" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P12" s="72" t="s">
+      <c r="P12" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q12" s="20"/>
@@ -15225,10 +14563,10 @@
       <c r="L13" s="20"/>
       <c r="M13" s="20"/>
       <c r="N13" s="20"/>
-      <c r="O13" s="72" t="s">
+      <c r="O13" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P13" s="72" t="s">
+      <c r="P13" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q13" s="20"/>
@@ -15281,10 +14619,10 @@
       <c r="L14" s="20"/>
       <c r="M14" s="20"/>
       <c r="N14" s="20"/>
-      <c r="O14" s="72" t="s">
+      <c r="O14" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P14" s="72" t="s">
+      <c r="P14" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q14" s="20"/>
@@ -15343,10 +14681,10 @@
       </c>
       <c r="M15" s="20"/>
       <c r="N15" s="20"/>
-      <c r="O15" s="72" t="s">
+      <c r="O15" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P15" s="72" t="s">
+      <c r="P15" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q15" s="28" t="s">
@@ -15411,10 +14749,10 @@
       </c>
       <c r="M16" s="20"/>
       <c r="N16" s="20"/>
-      <c r="O16" s="72" t="s">
+      <c r="O16" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P16" s="72" t="s">
+      <c r="P16" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q16" s="28" t="s">
@@ -15479,10 +14817,10 @@
       </c>
       <c r="M17" s="20"/>
       <c r="N17" s="20"/>
-      <c r="O17" s="72" t="s">
+      <c r="O17" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P17" s="72" t="s">
+      <c r="P17" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q17" s="28" t="s">
@@ -15547,10 +14885,10 @@
       </c>
       <c r="M18" s="20"/>
       <c r="N18" s="20"/>
-      <c r="O18" s="72" t="s">
+      <c r="O18" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P18" s="72" t="s">
+      <c r="P18" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q18" s="28" t="s">
@@ -15615,10 +14953,10 @@
       </c>
       <c r="M19" s="20"/>
       <c r="N19" s="20"/>
-      <c r="O19" s="72" t="s">
+      <c r="O19" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P19" s="72" t="s">
+      <c r="P19" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q19" s="28" t="s">
@@ -15683,10 +15021,10 @@
       </c>
       <c r="M20" s="20"/>
       <c r="N20" s="20"/>
-      <c r="O20" s="72" t="s">
+      <c r="O20" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P20" s="72" t="s">
+      <c r="P20" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q20" s="28" t="s">
@@ -15751,10 +15089,10 @@
       </c>
       <c r="M21" s="20"/>
       <c r="N21" s="20"/>
-      <c r="O21" s="72" t="s">
+      <c r="O21" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P21" s="72" t="s">
+      <c r="P21" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q21" s="28" t="s">
@@ -15813,10 +15151,10 @@
       <c r="L22" s="22"/>
       <c r="M22" s="22"/>
       <c r="N22" s="22"/>
-      <c r="O22" s="73" t="s">
+      <c r="O22" s="71" t="s">
         <v>536</v>
       </c>
-      <c r="P22" s="73" t="s">
+      <c r="P22" s="71" t="s">
         <v>529</v>
       </c>
       <c r="Q22" s="29"/>
@@ -15877,10 +15215,10 @@
       </c>
       <c r="M23" s="20"/>
       <c r="N23" s="20"/>
-      <c r="O23" s="72" t="s">
+      <c r="O23" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P23" s="72" t="s">
+      <c r="P23" s="70" t="s">
         <v>534</v>
       </c>
       <c r="Q23" s="28" t="s">
@@ -15945,10 +15283,10 @@
       </c>
       <c r="M24" s="20"/>
       <c r="N24" s="20"/>
-      <c r="O24" s="72" t="s">
+      <c r="O24" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P24" s="72" t="s">
+      <c r="P24" s="70" t="s">
         <v>534</v>
       </c>
       <c r="Q24" s="28" t="s">
@@ -16013,10 +15351,10 @@
       </c>
       <c r="M25" s="20"/>
       <c r="N25" s="20"/>
-      <c r="O25" s="72" t="s">
+      <c r="O25" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P25" s="72" t="s">
+      <c r="P25" s="70" t="s">
         <v>534</v>
       </c>
       <c r="Q25" s="28" t="s">
@@ -16081,10 +15419,10 @@
       </c>
       <c r="M26" s="20"/>
       <c r="N26" s="20"/>
-      <c r="O26" s="72" t="s">
+      <c r="O26" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P26" s="72" t="s">
+      <c r="P26" s="70" t="s">
         <v>534</v>
       </c>
       <c r="Q26" s="28" t="s">
@@ -16145,10 +15483,10 @@
       <c r="L27" s="21"/>
       <c r="M27" s="20"/>
       <c r="N27" s="20"/>
-      <c r="O27" s="72" t="s">
+      <c r="O27" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P27" s="72" t="s">
+      <c r="P27" s="70" t="s">
         <v>534</v>
       </c>
       <c r="Q27" s="20" t="s">
@@ -16205,10 +15543,10 @@
       <c r="L28" s="20"/>
       <c r="M28" s="20"/>
       <c r="N28" s="20"/>
-      <c r="O28" s="72" t="s">
+      <c r="O28" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P28" s="72" t="s">
+      <c r="P28" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q28" s="28"/>
@@ -16261,10 +15599,10 @@
       <c r="L29" s="20"/>
       <c r="M29" s="20"/>
       <c r="N29" s="20"/>
-      <c r="O29" s="72" t="s">
+      <c r="O29" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P29" s="72" t="s">
+      <c r="P29" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q29" s="28"/>
@@ -16317,10 +15655,10 @@
       <c r="L30" s="20"/>
       <c r="M30" s="20"/>
       <c r="N30" s="20"/>
-      <c r="O30" s="72" t="s">
+      <c r="O30" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P30" s="72" t="s">
+      <c r="P30" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q30" s="28"/>
@@ -16379,10 +15717,10 @@
       </c>
       <c r="M31" s="20"/>
       <c r="N31" s="20"/>
-      <c r="O31" s="72" t="s">
+      <c r="O31" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P31" s="72" t="s">
+      <c r="P31" s="70" t="s">
         <v>535</v>
       </c>
       <c r="Q31" s="28" t="s">
@@ -16447,10 +15785,10 @@
       </c>
       <c r="M32" s="20"/>
       <c r="N32" s="20"/>
-      <c r="O32" s="72" t="s">
+      <c r="O32" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P32" s="72" t="s">
+      <c r="P32" s="70" t="s">
         <v>535</v>
       </c>
       <c r="Q32" s="28" t="s">
@@ -16515,10 +15853,10 @@
       </c>
       <c r="M33" s="20"/>
       <c r="N33" s="20"/>
-      <c r="O33" s="72" t="s">
+      <c r="O33" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P33" s="72" t="s">
+      <c r="P33" s="70" t="s">
         <v>535</v>
       </c>
       <c r="Q33" s="28" t="s">
@@ -16583,10 +15921,10 @@
       </c>
       <c r="M34" s="20"/>
       <c r="N34" s="20"/>
-      <c r="O34" s="72" t="s">
+      <c r="O34" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P34" s="72" t="s">
+      <c r="P34" s="70" t="s">
         <v>535</v>
       </c>
       <c r="Q34" s="28" t="s">
@@ -16647,10 +15985,10 @@
       <c r="L35" s="21"/>
       <c r="M35" s="20"/>
       <c r="N35" s="20"/>
-      <c r="O35" s="72" t="s">
+      <c r="O35" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P35" s="72" t="s">
+      <c r="P35" s="70" t="s">
         <v>535</v>
       </c>
       <c r="Q35" s="28" t="s">
@@ -16707,10 +16045,10 @@
       <c r="L36" s="20"/>
       <c r="M36" s="20"/>
       <c r="N36" s="20"/>
-      <c r="O36" s="72" t="s">
+      <c r="O36" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P36" s="72" t="s">
+      <c r="P36" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q36" s="28"/>
@@ -16763,10 +16101,10 @@
       <c r="L37" s="20"/>
       <c r="M37" s="20"/>
       <c r="N37" s="20"/>
-      <c r="O37" s="72" t="s">
+      <c r="O37" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P37" s="72" t="s">
+      <c r="P37" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q37" s="28"/>
@@ -16819,10 +16157,10 @@
       <c r="L38" s="22"/>
       <c r="M38" s="22"/>
       <c r="N38" s="22"/>
-      <c r="O38" s="73" t="s">
+      <c r="O38" s="71" t="s">
         <v>536</v>
       </c>
-      <c r="P38" s="73" t="s">
+      <c r="P38" s="71" t="s">
         <v>529</v>
       </c>
       <c r="Q38" s="29"/>
@@ -16873,14 +16211,14 @@
       </c>
       <c r="K39" s="20"/>
       <c r="L39" s="20" t="s">
-        <v>192</v>
+        <v>537</v>
       </c>
       <c r="M39" s="20"/>
       <c r="N39" s="20"/>
-      <c r="O39" s="72" t="s">
+      <c r="O39" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P39" s="72" t="s">
+      <c r="P39" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q39" s="28" t="s">
@@ -16935,20 +16273,16 @@
         <v>236</v>
       </c>
       <c r="K40" s="20"/>
-      <c r="L40" s="20" t="s">
-        <v>193</v>
-      </c>
+      <c r="L40" s="20"/>
       <c r="M40" s="20"/>
       <c r="N40" s="20"/>
-      <c r="O40" s="72" t="s">
+      <c r="O40" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P40" s="72" t="s">
+      <c r="P40" s="70" t="s">
         <v>529</v>
       </c>
-      <c r="Q40" s="28" t="s">
-        <v>191</v>
-      </c>
+      <c r="Q40" s="28"/>
       <c r="R40" s="20"/>
       <c r="S40" s="20" t="s">
         <v>278</v>
@@ -16995,20 +16329,16 @@
         <v>251</v>
       </c>
       <c r="K41" s="20"/>
-      <c r="L41" s="20" t="s">
-        <v>264</v>
-      </c>
+      <c r="L41" s="20"/>
       <c r="M41" s="20"/>
       <c r="N41" s="20"/>
-      <c r="O41" s="72" t="s">
+      <c r="O41" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P41" s="72" t="s">
+      <c r="P41" s="70" t="s">
         <v>529</v>
       </c>
-      <c r="Q41" s="28" t="s">
-        <v>265</v>
-      </c>
+      <c r="Q41" s="28"/>
       <c r="R41" s="20"/>
       <c r="S41" s="20" t="s">
         <v>278</v>
@@ -17058,10 +16388,10 @@
       <c r="L42" s="20"/>
       <c r="M42" s="20"/>
       <c r="N42" s="20"/>
-      <c r="O42" s="72" t="s">
+      <c r="O42" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P42" s="72" t="s">
+      <c r="P42" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q42" s="28"/>
@@ -17114,10 +16444,10 @@
       <c r="L43" s="20"/>
       <c r="M43" s="20"/>
       <c r="N43" s="20"/>
-      <c r="O43" s="72" t="s">
+      <c r="O43" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P43" s="72" t="s">
+      <c r="P43" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q43" s="28"/>
@@ -17170,10 +16500,10 @@
       <c r="L44" s="20"/>
       <c r="M44" s="20"/>
       <c r="N44" s="20"/>
-      <c r="O44" s="72" t="s">
+      <c r="O44" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P44" s="72" t="s">
+      <c r="P44" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q44" s="28"/>
@@ -17226,10 +16556,10 @@
       <c r="L45" s="20"/>
       <c r="M45" s="20"/>
       <c r="N45" s="20"/>
-      <c r="O45" s="72" t="s">
+      <c r="O45" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P45" s="72" t="s">
+      <c r="P45" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q45" s="28"/>
@@ -17282,10 +16612,10 @@
       <c r="L46" s="20"/>
       <c r="M46" s="20"/>
       <c r="N46" s="20"/>
-      <c r="O46" s="72" t="s">
+      <c r="O46" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P46" s="72" t="s">
+      <c r="P46" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q46" s="28"/>
@@ -17338,10 +16668,10 @@
       <c r="L47" s="20"/>
       <c r="M47" s="20"/>
       <c r="N47" s="20"/>
-      <c r="O47" s="72" t="s">
+      <c r="O47" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P47" s="72" t="s">
+      <c r="P47" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q47" s="28"/>
@@ -17394,10 +16724,10 @@
       <c r="L48" s="20"/>
       <c r="M48" s="20"/>
       <c r="N48" s="20"/>
-      <c r="O48" s="72" t="s">
+      <c r="O48" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P48" s="72" t="s">
+      <c r="P48" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q48" s="28"/>
@@ -17450,10 +16780,10 @@
       <c r="L49" s="20"/>
       <c r="M49" s="20"/>
       <c r="N49" s="20"/>
-      <c r="O49" s="72" t="s">
+      <c r="O49" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P49" s="72" t="s">
+      <c r="P49" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q49" s="28"/>
@@ -17506,10 +16836,10 @@
       <c r="L50" s="20"/>
       <c r="M50" s="20"/>
       <c r="N50" s="20"/>
-      <c r="O50" s="72" t="s">
+      <c r="O50" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P50" s="72" t="s">
+      <c r="P50" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q50" s="28"/>
@@ -17562,10 +16892,10 @@
       <c r="L51" s="20"/>
       <c r="M51" s="20"/>
       <c r="N51" s="20"/>
-      <c r="O51" s="72" t="s">
+      <c r="O51" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P51" s="72" t="s">
+      <c r="P51" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q51" s="28"/>
@@ -17618,10 +16948,10 @@
       <c r="L52" s="20"/>
       <c r="M52" s="20"/>
       <c r="N52" s="20"/>
-      <c r="O52" s="72" t="s">
+      <c r="O52" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P52" s="72" t="s">
+      <c r="P52" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q52" s="20"/>
@@ -17674,10 +17004,10 @@
       <c r="L53" s="20"/>
       <c r="M53" s="20"/>
       <c r="N53" s="20"/>
-      <c r="O53" s="72" t="s">
+      <c r="O53" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P53" s="72" t="s">
+      <c r="P53" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q53" s="20"/>
@@ -17730,10 +17060,10 @@
       <c r="L54" s="22"/>
       <c r="M54" s="22"/>
       <c r="N54" s="22"/>
-      <c r="O54" s="73" t="s">
+      <c r="O54" s="71" t="s">
         <v>536</v>
       </c>
-      <c r="P54" s="73" t="s">
+      <c r="P54" s="71" t="s">
         <v>529</v>
       </c>
       <c r="Q54" s="22"/>
@@ -17792,10 +17122,10 @@
       </c>
       <c r="M55" s="20"/>
       <c r="N55" s="20"/>
-      <c r="O55" s="72" t="s">
+      <c r="O55" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P55" s="72" t="s">
+      <c r="P55" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q55" s="28" t="s">
@@ -17860,10 +17190,10 @@
       </c>
       <c r="M56" s="20"/>
       <c r="N56" s="20"/>
-      <c r="O56" s="72" t="s">
+      <c r="O56" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P56" s="72" t="s">
+      <c r="P56" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q56" s="28" t="s">
@@ -17926,10 +17256,10 @@
       <c r="L57" s="20"/>
       <c r="M57" s="20"/>
       <c r="N57" s="20"/>
-      <c r="O57" s="72" t="s">
+      <c r="O57" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P57" s="72" t="s">
+      <c r="P57" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q57" s="28" t="s">
@@ -17990,10 +17320,10 @@
       </c>
       <c r="M58" s="20"/>
       <c r="N58" s="20"/>
-      <c r="O58" s="72" t="s">
+      <c r="O58" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P58" s="72" t="s">
+      <c r="P58" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q58" s="67" t="s">
@@ -18054,10 +17384,10 @@
       </c>
       <c r="M59" s="20"/>
       <c r="N59" s="20"/>
-      <c r="O59" s="72" t="s">
+      <c r="O59" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P59" s="72" t="s">
+      <c r="P59" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q59" s="28" t="s">
@@ -18122,10 +17452,10 @@
       </c>
       <c r="M60" s="20"/>
       <c r="N60" s="20"/>
-      <c r="O60" s="72" t="s">
+      <c r="O60" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P60" s="72" t="s">
+      <c r="P60" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q60" s="28" t="s">
@@ -18188,10 +17518,10 @@
       </c>
       <c r="M61" s="20"/>
       <c r="N61" s="20"/>
-      <c r="O61" s="72" t="s">
+      <c r="O61" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P61" s="72" t="s">
+      <c r="P61" s="70" t="s">
         <v>529</v>
       </c>
       <c r="Q61" s="28" t="s">
@@ -18252,10 +17582,10 @@
       </c>
       <c r="M62" s="22"/>
       <c r="N62" s="22"/>
-      <c r="O62" s="73" t="s">
+      <c r="O62" s="71" t="s">
         <v>536</v>
       </c>
-      <c r="P62" s="73" t="s">
+      <c r="P62" s="71" t="s">
         <v>529</v>
       </c>
       <c r="Q62" s="67" t="s">
@@ -18312,10 +17642,10 @@
       <c r="L63" s="32"/>
       <c r="M63" s="32"/>
       <c r="N63" s="32"/>
-      <c r="O63" s="71" t="s">
+      <c r="O63" s="69" t="s">
         <v>536</v>
       </c>
-      <c r="P63" s="71" t="s">
+      <c r="P63" s="69" t="s">
         <v>528</v>
       </c>
       <c r="Q63" s="33" t="s">
@@ -18382,10 +17712,10 @@
       <c r="L64" s="20"/>
       <c r="M64" s="20"/>
       <c r="N64" s="20"/>
-      <c r="O64" s="72" t="s">
+      <c r="O64" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P64" s="72" t="s">
+      <c r="P64" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q64" s="28" t="s">
@@ -18447,10 +17777,10 @@
       <c r="L65" s="20"/>
       <c r="M65" s="20"/>
       <c r="N65" s="20"/>
-      <c r="O65" s="72" t="s">
+      <c r="O65" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P65" s="72" t="s">
+      <c r="P65" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q65" s="28" t="s">
@@ -18509,10 +17839,10 @@
       <c r="L66" s="20"/>
       <c r="M66" s="20"/>
       <c r="N66" s="20"/>
-      <c r="O66" s="72" t="s">
+      <c r="O66" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P66" s="72" t="s">
+      <c r="P66" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q66" s="28" t="s">
@@ -18571,10 +17901,10 @@
       <c r="L67" s="20"/>
       <c r="M67" s="20"/>
       <c r="N67" s="20"/>
-      <c r="O67" s="72" t="s">
+      <c r="O67" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P67" s="72" t="s">
+      <c r="P67" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q67" s="28" t="s">
@@ -18631,10 +17961,10 @@
       <c r="L68" s="20"/>
       <c r="M68" s="20"/>
       <c r="N68" s="20"/>
-      <c r="O68" s="72" t="s">
+      <c r="O68" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P68" s="72" t="s">
+      <c r="P68" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q68" s="28"/>
@@ -18687,10 +18017,10 @@
       <c r="L69" s="20"/>
       <c r="M69" s="20"/>
       <c r="N69" s="20"/>
-      <c r="O69" s="72" t="s">
+      <c r="O69" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P69" s="72" t="s">
+      <c r="P69" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q69" s="28"/>
@@ -18743,10 +18073,10 @@
       <c r="L70" s="20"/>
       <c r="M70" s="20"/>
       <c r="N70" s="20"/>
-      <c r="O70" s="72" t="s">
+      <c r="O70" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P70" s="72" t="s">
+      <c r="P70" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q70" s="28"/>
@@ -18799,10 +18129,10 @@
       <c r="L71" s="20"/>
       <c r="M71" s="20"/>
       <c r="N71" s="20"/>
-      <c r="O71" s="72" t="s">
+      <c r="O71" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P71" s="72" t="s">
+      <c r="P71" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q71" s="28"/>
@@ -18861,10 +18191,10 @@
       </c>
       <c r="M72" s="20"/>
       <c r="N72" s="20"/>
-      <c r="O72" s="72" t="s">
+      <c r="O72" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P72" s="72" t="s">
+      <c r="P72" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q72" s="28" t="s">
@@ -18929,10 +18259,10 @@
       </c>
       <c r="M73" s="20"/>
       <c r="N73" s="20"/>
-      <c r="O73" s="72" t="s">
+      <c r="O73" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P73" s="72" t="s">
+      <c r="P73" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q73" s="28" t="s">
@@ -18991,10 +18321,10 @@
       <c r="L74" s="20"/>
       <c r="M74" s="20"/>
       <c r="N74" s="20"/>
-      <c r="O74" s="72" t="s">
+      <c r="O74" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P74" s="72" t="s">
+      <c r="P74" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q74" s="28"/>
@@ -19047,10 +18377,10 @@
       <c r="L75" s="20"/>
       <c r="M75" s="20"/>
       <c r="N75" s="20"/>
-      <c r="O75" s="72" t="s">
+      <c r="O75" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P75" s="72" t="s">
+      <c r="P75" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q75" s="28"/>
@@ -19103,10 +18433,10 @@
       <c r="L76" s="20"/>
       <c r="M76" s="20"/>
       <c r="N76" s="20"/>
-      <c r="O76" s="72" t="s">
+      <c r="O76" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P76" s="72" t="s">
+      <c r="P76" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q76" s="28"/>
@@ -19159,10 +18489,10 @@
       <c r="L77" s="20"/>
       <c r="M77" s="20"/>
       <c r="N77" s="20"/>
-      <c r="O77" s="72" t="s">
+      <c r="O77" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P77" s="72" t="s">
+      <c r="P77" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q77" s="28"/>
@@ -19219,10 +18549,10 @@
       </c>
       <c r="M78" s="20"/>
       <c r="N78" s="20"/>
-      <c r="O78" s="72" t="s">
+      <c r="O78" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P78" s="72" t="s">
+      <c r="P78" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q78" s="28" t="s">
@@ -19281,10 +18611,10 @@
       </c>
       <c r="M79" s="22"/>
       <c r="N79" s="22"/>
-      <c r="O79" s="73" t="s">
+      <c r="O79" s="71" t="s">
         <v>536</v>
       </c>
-      <c r="P79" s="73" t="s">
+      <c r="P79" s="71" t="s">
         <v>528</v>
       </c>
       <c r="Q79" s="29" t="s">
@@ -19341,7 +18671,7 @@
       </c>
       <c r="M80" s="20"/>
       <c r="N80" s="20"/>
-      <c r="O80" s="72" t="s">
+      <c r="O80" s="70" t="s">
         <v>536</v>
       </c>
       <c r="P80" s="56" t="s">
@@ -19401,7 +18731,7 @@
       </c>
       <c r="M81" s="20"/>
       <c r="N81" s="20"/>
-      <c r="O81" s="72" t="s">
+      <c r="O81" s="70" t="s">
         <v>536</v>
       </c>
       <c r="P81" s="56" t="s">
@@ -19459,10 +18789,10 @@
       <c r="L82" s="20"/>
       <c r="M82" s="20"/>
       <c r="N82" s="20"/>
-      <c r="O82" s="72" t="s">
+      <c r="O82" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P82" s="72" t="s">
+      <c r="P82" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q82" s="28"/>
@@ -19515,10 +18845,10 @@
       <c r="L83" s="20"/>
       <c r="M83" s="20"/>
       <c r="N83" s="20"/>
-      <c r="O83" s="72" t="s">
+      <c r="O83" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P83" s="72" t="s">
+      <c r="P83" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q83" s="28"/>
@@ -19571,10 +18901,10 @@
       <c r="L84" s="20"/>
       <c r="M84" s="20"/>
       <c r="N84" s="20"/>
-      <c r="O84" s="72" t="s">
+      <c r="O84" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P84" s="72" t="s">
+      <c r="P84" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q84" s="28"/>
@@ -19627,10 +18957,10 @@
       <c r="L85" s="20"/>
       <c r="M85" s="20"/>
       <c r="N85" s="20"/>
-      <c r="O85" s="72" t="s">
+      <c r="O85" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P85" s="72" t="s">
+      <c r="P85" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q85" s="28"/>
@@ -19683,10 +19013,10 @@
       <c r="L86" s="20"/>
       <c r="M86" s="20"/>
       <c r="N86" s="20"/>
-      <c r="O86" s="72" t="s">
+      <c r="O86" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P86" s="72" t="s">
+      <c r="P86" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q86" s="28"/>
@@ -19739,10 +19069,10 @@
       <c r="L87" s="20"/>
       <c r="M87" s="20"/>
       <c r="N87" s="20"/>
-      <c r="O87" s="72" t="s">
+      <c r="O87" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P87" s="72" t="s">
+      <c r="P87" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q87" s="28"/>
@@ -19795,10 +19125,10 @@
       <c r="L88" s="20"/>
       <c r="M88" s="20"/>
       <c r="N88" s="20"/>
-      <c r="O88" s="72" t="s">
+      <c r="O88" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P88" s="72" t="s">
+      <c r="P88" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q88" s="28"/>
@@ -19851,10 +19181,10 @@
       <c r="L89" s="20"/>
       <c r="M89" s="20"/>
       <c r="N89" s="20"/>
-      <c r="O89" s="72" t="s">
+      <c r="O89" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P89" s="72" t="s">
+      <c r="P89" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q89" s="28"/>
@@ -19907,10 +19237,10 @@
       <c r="L90" s="20"/>
       <c r="M90" s="20"/>
       <c r="N90" s="20"/>
-      <c r="O90" s="72" t="s">
+      <c r="O90" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P90" s="72" t="s">
+      <c r="P90" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q90" s="28"/>
@@ -19963,10 +19293,10 @@
       <c r="L91" s="20"/>
       <c r="M91" s="20"/>
       <c r="N91" s="20"/>
-      <c r="O91" s="72" t="s">
+      <c r="O91" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P91" s="72" t="s">
+      <c r="P91" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q91" s="28"/>
@@ -20019,10 +19349,10 @@
       <c r="L92" s="20"/>
       <c r="M92" s="20"/>
       <c r="N92" s="20"/>
-      <c r="O92" s="72" t="s">
+      <c r="O92" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P92" s="72" t="s">
+      <c r="P92" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q92" s="28"/>
@@ -20075,10 +19405,10 @@
       <c r="L93" s="20"/>
       <c r="M93" s="20"/>
       <c r="N93" s="20"/>
-      <c r="O93" s="72" t="s">
+      <c r="O93" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P93" s="72" t="s">
+      <c r="P93" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q93" s="28"/>
@@ -20131,10 +19461,10 @@
       <c r="L94" s="20"/>
       <c r="M94" s="20"/>
       <c r="N94" s="20"/>
-      <c r="O94" s="72" t="s">
+      <c r="O94" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P94" s="72" t="s">
+      <c r="P94" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q94" s="28"/>
@@ -20187,10 +19517,10 @@
       <c r="L95" s="22"/>
       <c r="M95" s="22"/>
       <c r="N95" s="22"/>
-      <c r="O95" s="73" t="s">
+      <c r="O95" s="71" t="s">
         <v>536</v>
       </c>
-      <c r="P95" s="73" t="s">
+      <c r="P95" s="71" t="s">
         <v>528</v>
       </c>
       <c r="Q95" s="29"/>
@@ -20249,10 +19579,10 @@
       </c>
       <c r="M96" s="20"/>
       <c r="N96" s="20"/>
-      <c r="O96" s="72" t="s">
+      <c r="O96" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P96" s="72" t="s">
+      <c r="P96" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q96" s="37" t="s">
@@ -20315,10 +19645,10 @@
       </c>
       <c r="M97" s="20"/>
       <c r="N97" s="20"/>
-      <c r="O97" s="72" t="s">
+      <c r="O97" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P97" s="72" t="s">
+      <c r="P97" s="70" t="s">
         <v>530</v>
       </c>
       <c r="Q97" s="28" t="s">
@@ -20377,10 +19707,10 @@
       <c r="L98" s="20"/>
       <c r="M98" s="20"/>
       <c r="N98" s="20"/>
-      <c r="O98" s="72" t="s">
+      <c r="O98" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P98" s="72" t="s">
+      <c r="P98" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q98" s="37"/>
@@ -20433,10 +19763,10 @@
       <c r="L99" s="20"/>
       <c r="M99" s="20"/>
       <c r="N99" s="20"/>
-      <c r="O99" s="72" t="s">
+      <c r="O99" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P99" s="72" t="s">
+      <c r="P99" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q99" s="37"/>
@@ -20495,10 +19825,10 @@
       </c>
       <c r="M100" s="20"/>
       <c r="N100" s="20"/>
-      <c r="O100" s="72" t="s">
+      <c r="O100" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P100" s="72" t="s">
+      <c r="P100" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q100" s="66" t="s">
@@ -20561,10 +19891,10 @@
       </c>
       <c r="M101" s="20"/>
       <c r="N101" s="20"/>
-      <c r="O101" s="72" t="s">
+      <c r="O101" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P101" s="72" t="s">
+      <c r="P101" s="70" t="s">
         <v>530</v>
       </c>
       <c r="Q101" s="28" t="s">
@@ -20623,10 +19953,10 @@
       <c r="L102" s="20"/>
       <c r="M102" s="20"/>
       <c r="N102" s="20"/>
-      <c r="O102" s="72" t="s">
+      <c r="O102" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P102" s="72" t="s">
+      <c r="P102" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q102" s="28"/>
@@ -20679,10 +20009,10 @@
       <c r="L103" s="22"/>
       <c r="M103" s="22"/>
       <c r="N103" s="22"/>
-      <c r="O103" s="73" t="s">
+      <c r="O103" s="71" t="s">
         <v>536</v>
       </c>
-      <c r="P103" s="73" t="s">
+      <c r="P103" s="71" t="s">
         <v>528</v>
       </c>
       <c r="Q103" s="29"/>
@@ -20739,10 +20069,10 @@
       </c>
       <c r="M104" s="20"/>
       <c r="N104" s="20"/>
-      <c r="O104" s="72" t="s">
+      <c r="O104" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P104" s="72" t="s">
+      <c r="P104" s="70" t="s">
         <v>531</v>
       </c>
       <c r="Q104" s="37" t="s">
@@ -20799,10 +20129,10 @@
       <c r="L105" s="38"/>
       <c r="M105" s="20"/>
       <c r="N105" s="20"/>
-      <c r="O105" s="72" t="s">
+      <c r="O105" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P105" s="72" t="s">
+      <c r="P105" s="70" t="s">
         <v>531</v>
       </c>
       <c r="Q105" s="37" t="s">
@@ -20861,10 +20191,10 @@
       </c>
       <c r="M106" s="20"/>
       <c r="N106" s="20"/>
-      <c r="O106" s="72" t="s">
+      <c r="O106" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P106" s="72" t="s">
+      <c r="P106" s="70" t="s">
         <v>532</v>
       </c>
       <c r="Q106" s="37" t="s">
@@ -20921,10 +20251,10 @@
       <c r="L107" s="38"/>
       <c r="M107" s="20"/>
       <c r="N107" s="20"/>
-      <c r="O107" s="72" t="s">
+      <c r="O107" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P107" s="72" t="s">
+      <c r="P107" s="70" t="s">
         <v>532</v>
       </c>
       <c r="Q107" s="37" t="s">
@@ -20983,10 +20313,10 @@
       </c>
       <c r="M108" s="20"/>
       <c r="N108" s="20"/>
-      <c r="O108" s="72" t="s">
+      <c r="O108" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P108" s="72" t="s">
+      <c r="P108" s="70" t="s">
         <v>531</v>
       </c>
       <c r="Q108" s="37" t="s">
@@ -21043,10 +20373,10 @@
       </c>
       <c r="M109" s="20"/>
       <c r="N109" s="20"/>
-      <c r="O109" s="72" t="s">
+      <c r="O109" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P109" s="72" t="s">
+      <c r="P109" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q109" s="37" t="s">
@@ -21105,10 +20435,10 @@
       </c>
       <c r="M110" s="20"/>
       <c r="N110" s="20"/>
-      <c r="O110" s="72" t="s">
+      <c r="O110" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P110" s="72" t="s">
+      <c r="P110" s="70" t="s">
         <v>532</v>
       </c>
       <c r="Q110" s="37" t="s">
@@ -21165,10 +20495,10 @@
       </c>
       <c r="M111" s="22"/>
       <c r="N111" s="22"/>
-      <c r="O111" s="73" t="s">
+      <c r="O111" s="71" t="s">
         <v>536</v>
       </c>
-      <c r="P111" s="73" t="s">
+      <c r="P111" s="71" t="s">
         <v>528</v>
       </c>
       <c r="Q111" s="40" t="s">
@@ -21227,10 +20557,10 @@
       </c>
       <c r="M112" s="20"/>
       <c r="N112" s="20"/>
-      <c r="O112" s="72" t="s">
+      <c r="O112" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P112" s="72" t="s">
+      <c r="P112" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q112" s="28" t="s">
@@ -21292,10 +20622,10 @@
       </c>
       <c r="M113" s="20"/>
       <c r="N113" s="20"/>
-      <c r="O113" s="72" t="s">
+      <c r="O113" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P113" s="72" t="s">
+      <c r="P113" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q113" s="37" t="s">
@@ -21354,10 +20684,10 @@
       </c>
       <c r="M114" s="20"/>
       <c r="N114" s="20"/>
-      <c r="O114" s="72" t="s">
+      <c r="O114" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P114" s="72" t="s">
+      <c r="P114" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q114" s="28" t="s">
@@ -21416,10 +20746,10 @@
       </c>
       <c r="M115" s="22"/>
       <c r="N115" s="22"/>
-      <c r="O115" s="73" t="s">
+      <c r="O115" s="71" t="s">
         <v>536</v>
       </c>
-      <c r="P115" s="73" t="s">
+      <c r="P115" s="71" t="s">
         <v>528</v>
       </c>
       <c r="Q115" s="29" t="s">
@@ -21478,10 +20808,10 @@
       </c>
       <c r="M116" s="20"/>
       <c r="N116" s="20"/>
-      <c r="O116" s="72" t="s">
+      <c r="O116" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P116" s="72" t="s">
+      <c r="P116" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q116" s="28" t="s">
@@ -21536,10 +20866,10 @@
       <c r="L117" s="20"/>
       <c r="M117" s="20"/>
       <c r="N117" s="20"/>
-      <c r="O117" s="72" t="s">
+      <c r="O117" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P117" s="72" t="s">
+      <c r="P117" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q117" s="37"/>
@@ -21592,10 +20922,10 @@
       <c r="L118" s="38"/>
       <c r="M118" s="20"/>
       <c r="N118" s="20"/>
-      <c r="O118" s="72" t="s">
+      <c r="O118" s="70" t="s">
         <v>536</v>
       </c>
-      <c r="P118" s="72" t="s">
+      <c r="P118" s="70" t="s">
         <v>528</v>
       </c>
       <c r="Q118" s="28"/>
@@ -21648,10 +20978,10 @@
       <c r="L119" s="39"/>
       <c r="M119" s="22"/>
       <c r="N119" s="22"/>
-      <c r="O119" s="73" t="s">
+      <c r="O119" s="71" t="s">
         <v>536</v>
       </c>
-      <c r="P119" s="73" t="s">
+      <c r="P119" s="71" t="s">
         <v>528</v>
       </c>
       <c r="Q119" s="29"/>
@@ -21706,10 +21036,10 @@
       <c r="L120" s="18"/>
       <c r="M120" s="18"/>
       <c r="N120" s="18"/>
-      <c r="O120" s="74" t="s">
+      <c r="O120" s="72" t="s">
         <v>536</v>
       </c>
-      <c r="P120" s="74" t="s">
+      <c r="P120" s="72" t="s">
         <v>533</v>
       </c>
       <c r="Q120" s="18" t="s">
@@ -21778,7 +21108,7 @@
       <c r="L121" s="20"/>
       <c r="M121" s="20"/>
       <c r="N121" s="20"/>
-      <c r="O121" s="72" t="s">
+      <c r="O121" s="70" t="s">
         <v>536</v>
       </c>
       <c r="P121" s="28"/>
@@ -21836,7 +21166,7 @@
       <c r="L122" s="20"/>
       <c r="M122" s="20"/>
       <c r="N122" s="20"/>
-      <c r="O122" s="72" t="s">
+      <c r="O122" s="70" t="s">
         <v>536</v>
       </c>
       <c r="P122" s="28"/>
@@ -21894,7 +21224,7 @@
       <c r="L123" s="20"/>
       <c r="M123" s="20"/>
       <c r="N123" s="20"/>
-      <c r="O123" s="72" t="s">
+      <c r="O123" s="70" t="s">
         <v>536</v>
       </c>
       <c r="P123" s="28"/>
@@ -21952,7 +21282,7 @@
       <c r="L124" s="20"/>
       <c r="M124" s="20"/>
       <c r="N124" s="20"/>
-      <c r="O124" s="72" t="s">
+      <c r="O124" s="70" t="s">
         <v>536</v>
       </c>
       <c r="P124" s="28"/>
@@ -22010,7 +21340,7 @@
       <c r="L125" s="20"/>
       <c r="M125" s="20"/>
       <c r="N125" s="20"/>
-      <c r="O125" s="72" t="s">
+      <c r="O125" s="70" t="s">
         <v>536</v>
       </c>
       <c r="P125" s="28"/>
@@ -22068,7 +21398,7 @@
       <c r="L126" s="20"/>
       <c r="M126" s="20"/>
       <c r="N126" s="20"/>
-      <c r="O126" s="72" t="s">
+      <c r="O126" s="70" t="s">
         <v>536</v>
       </c>
       <c r="P126" s="28"/>
@@ -22126,7 +21456,7 @@
       <c r="L127" s="20"/>
       <c r="M127" s="20"/>
       <c r="N127" s="20"/>
-      <c r="O127" s="72" t="s">
+      <c r="O127" s="70" t="s">
         <v>536</v>
       </c>
       <c r="P127" s="28"/>
@@ -22184,7 +21514,7 @@
       <c r="L128" s="20"/>
       <c r="M128" s="20"/>
       <c r="N128" s="20"/>
-      <c r="O128" s="72" t="s">
+      <c r="O128" s="70" t="s">
         <v>536</v>
       </c>
       <c r="P128" s="28"/>
@@ -22242,7 +21572,7 @@
       <c r="L129" s="20"/>
       <c r="M129" s="20"/>
       <c r="N129" s="20"/>
-      <c r="O129" s="72" t="s">
+      <c r="O129" s="70" t="s">
         <v>536</v>
       </c>
       <c r="P129" s="28"/>
@@ -22300,7 +21630,7 @@
       <c r="L130" s="20"/>
       <c r="M130" s="20"/>
       <c r="N130" s="20"/>
-      <c r="O130" s="72" t="s">
+      <c r="O130" s="70" t="s">
         <v>536</v>
       </c>
       <c r="P130" s="28"/>
@@ -22358,7 +21688,7 @@
       <c r="L131" s="20"/>
       <c r="M131" s="20"/>
       <c r="N131" s="20"/>
-      <c r="O131" s="72" t="s">
+      <c r="O131" s="70" t="s">
         <v>536</v>
       </c>
       <c r="P131" s="28"/>
@@ -22416,7 +21746,7 @@
       <c r="L132" s="20"/>
       <c r="M132" s="20"/>
       <c r="N132" s="20"/>
-      <c r="O132" s="72" t="s">
+      <c r="O132" s="70" t="s">
         <v>536</v>
       </c>
       <c r="P132" s="28"/>
@@ -22474,7 +21804,7 @@
       <c r="L133" s="20"/>
       <c r="M133" s="20"/>
       <c r="N133" s="20"/>
-      <c r="O133" s="72" t="s">
+      <c r="O133" s="70" t="s">
         <v>536</v>
       </c>
       <c r="P133" s="28"/>
@@ -22532,7 +21862,7 @@
       <c r="L134" s="20"/>
       <c r="M134" s="20"/>
       <c r="N134" s="20"/>
-      <c r="O134" s="72" t="s">
+      <c r="O134" s="70" t="s">
         <v>536</v>
       </c>
       <c r="P134" s="28"/>
@@ -22590,7 +21920,7 @@
       <c r="L135" s="20"/>
       <c r="M135" s="20"/>
       <c r="N135" s="20"/>
-      <c r="O135" s="72" t="s">
+      <c r="O135" s="70" t="s">
         <v>536</v>
       </c>
       <c r="P135" s="28"/>
@@ -22648,7 +21978,7 @@
       <c r="L136" s="22"/>
       <c r="M136" s="22"/>
       <c r="N136" s="22"/>
-      <c r="O136" s="73" t="s">
+      <c r="O136" s="71" t="s">
         <v>536</v>
       </c>
       <c r="P136" s="29"/>
@@ -22863,243 +22193,243 @@
   <autoFilter ref="A1:AF9235" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <dataConsolidate/>
   <conditionalFormatting sqref="A80:A119 K98:P100 K102:P113 K116:P117">
-    <cfRule type="expression" dxfId="80" priority="13" stopIfTrue="1">
+    <cfRule type="expression" dxfId="48" priority="13" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A120:P120 U120 X120:AC120">
-    <cfRule type="expression" dxfId="79" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="47" priority="7" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E6:T6 V6:W6 A3:W5 Y3:AC5">
-    <cfRule type="expression" dxfId="78" priority="41" stopIfTrue="1">
+  <conditionalFormatting sqref="A3:W5 Y3:AC5 E6:T6 V6:W6">
+    <cfRule type="expression" dxfId="46" priority="41" stopIfTrue="1">
       <formula>$X3="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:X2">
-    <cfRule type="expression" dxfId="77" priority="48" stopIfTrue="1">
+    <cfRule type="expression" dxfId="45" priority="48" stopIfTrue="1">
       <formula>$Y1="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A121:AC136">
-    <cfRule type="expression" dxfId="76" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="44" priority="8" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6">
-    <cfRule type="expression" dxfId="75" priority="31" stopIfTrue="1">
+    <cfRule type="expression" dxfId="43" priority="31" stopIfTrue="1">
       <formula>$X6="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B63">
-    <cfRule type="expression" dxfId="74" priority="26" stopIfTrue="1">
+    <cfRule type="expression" dxfId="42" priority="26" stopIfTrue="1">
       <formula>$X63="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E63">
-    <cfRule type="expression" dxfId="73" priority="27" stopIfTrue="1">
+    <cfRule type="expression" dxfId="41" priority="27" stopIfTrue="1">
       <formula>$X63="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E63:H63">
-    <cfRule type="expression" dxfId="72" priority="28" stopIfTrue="1">
+    <cfRule type="expression" dxfId="40" priority="28" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:Q6 U6 X6:AC6">
-    <cfRule type="expression" dxfId="71" priority="47" stopIfTrue="1">
+    <cfRule type="expression" dxfId="39" priority="47" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G119">
+    <cfRule type="duplicateValues" dxfId="38" priority="1368"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="G120:G136">
-    <cfRule type="duplicateValues" dxfId="70" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I63 V63:W63">
-    <cfRule type="expression" dxfId="69" priority="33" stopIfTrue="1">
+    <cfRule type="expression" dxfId="36" priority="33" stopIfTrue="1">
       <formula>$X63="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I63:Q63">
-    <cfRule type="expression" dxfId="68" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="35" priority="22" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7:J54 D7:I62 K8:N26 O8:O38 P15:AC54 D64:I119">
-    <cfRule type="expression" dxfId="67" priority="34" stopIfTrue="1">
+    <cfRule type="expression" dxfId="34" priority="34" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J64:J95">
-    <cfRule type="expression" dxfId="66" priority="25" stopIfTrue="1">
+    <cfRule type="expression" dxfId="33" priority="25" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27 M27:N27 K28:N30 M31:N35 K36:N38">
-    <cfRule type="expression" dxfId="65" priority="39" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="39" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K31:K35">
-    <cfRule type="expression" dxfId="64" priority="30" stopIfTrue="1">
+    <cfRule type="expression" dxfId="31" priority="30" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K111">
-    <cfRule type="expression" dxfId="63" priority="17" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="17" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39:O56 A39:A62 P55:X56 K57:Q57 S57:X57 M58:P58 S58:T58 V58:X58 K59:X60">
-    <cfRule type="expression" dxfId="62" priority="36" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="36" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K64:P96">
-    <cfRule type="expression" dxfId="61" priority="21" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="21" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K61:Q61 S61:X61">
-    <cfRule type="expression" dxfId="60" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="1" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K114:Q115 K118:Q119">
-    <cfRule type="expression" dxfId="59" priority="19" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="19" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7:AC7 Q8:AC11 Q12:V12 X12:AC12 Q13:AC14">
-    <cfRule type="expression" dxfId="58" priority="38" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="38" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K97:AC97">
-    <cfRule type="expression" dxfId="57" priority="12" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="12" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K101:AC101">
-    <cfRule type="expression" dxfId="56" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="11" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L31:L34">
-    <cfRule type="expression" dxfId="55" priority="29" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="29" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L106">
-    <cfRule type="expression" dxfId="54" priority="18" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="18" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L110:L111">
-    <cfRule type="expression" dxfId="53" priority="16" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="16" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M62:P62 R62:X62">
-    <cfRule type="expression" dxfId="52" priority="35" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="35" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P8:P14">
-    <cfRule type="expression" dxfId="51" priority="37" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="37" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q73:Q95">
-    <cfRule type="expression" dxfId="50" priority="14" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="14" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q112">
-    <cfRule type="expression" dxfId="49" priority="20" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="20" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q116">
-    <cfRule type="expression" dxfId="48" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="2" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q120:T120">
-    <cfRule type="expression" dxfId="47" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="9" stopIfTrue="1">
       <formula>$X120="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q64:X72">
-    <cfRule type="expression" dxfId="46" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="3" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q102:X103">
-    <cfRule type="expression" dxfId="45" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="23" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R104:S111 U104:W111">
-    <cfRule type="expression" dxfId="44" priority="32" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="32" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R63:T63">
-    <cfRule type="expression" dxfId="43" priority="44" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="44" stopIfTrue="1">
       <formula>$X63="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R73:X77 R78:S81 U78:X81 R82:X96 R98:AC100">
-    <cfRule type="expression" dxfId="42" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="24" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R112:AC119">
-    <cfRule type="expression" dxfId="41" priority="40" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="40" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T78:T79">
-    <cfRule type="expression" dxfId="40" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="15" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U63 X63:AC63">
-    <cfRule type="expression" dxfId="39" priority="45" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="45" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V120:W120">
-    <cfRule type="expression" dxfId="38" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="10" stopIfTrue="1">
       <formula>$X120="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X3:X5">
-    <cfRule type="expression" dxfId="37" priority="42" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="42" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y1:AC2">
-    <cfRule type="expression" dxfId="36" priority="49" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="49" stopIfTrue="1">
       <formula>$X1="PA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y55:AC62 Y64:AC96 Y102:AC105 X104:X105 X106:AC111">
-    <cfRule type="expression" dxfId="35" priority="46" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="46" stopIfTrue="1">
       <formula>#REF!="PA"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G119">
-    <cfRule type="duplicateValues" dxfId="34" priority="1368"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="AD1:AD119 AD137:AD142">
-    <cfRule type="expression" dxfId="33" priority="1371">
+    <cfRule type="expression" dxfId="1" priority="1371">
       <formula>IF($AD1&lt;&gt;"", SUM(--(($AC1 &amp;"-" &amp;$AD1)=(_xlfn._TRO_TRAILING($AC$1:$AC$9234) &amp;"-" &amp;_xlfn._TRO_TRAILING($AD$1:$AD$9234))))&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD120:AD136">
-    <cfRule type="expression" dxfId="32" priority="1374">
+    <cfRule type="expression" dxfId="0" priority="1374">
       <formula>IF($AD120&lt;&gt;"", SUM(--(($AC120 &amp;"-" &amp;$AD120)=(_xlfn._TRO_TRAILING($AC$1:$AC$10002) &amp;"-" &amp;_xlfn._TRO_TRAILING($AD$1:$AD$10002))))&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Shared/DocumentsValidationData/Passing/8XXX_IOyyyy_R0.0_EmergencyIoListValidationTemplate.xlsx
+++ b/Shared/DocumentsValidationData/Passing/8XXX_IOyyyy_R0.0_EmergencyIoListValidationTemplate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Source\Repos\_Openn2\Shared\DocumentsValidationData\Passing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_BBCC8C8EB05E46D6770C3C46292C72E8027F9B93" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1506A6E2-E885-4AD2-A531-20F7B150DBA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17790" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17790" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="COVER" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6497" uniqueCount="974">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6499" uniqueCount="975">
   <si>
     <t>Source</t>
   </si>
@@ -2975,6 +2975,9 @@
   </si>
   <si>
     <t>PNC_Q_Encoder Speed [ =S2+PC2.CC1-X81001 ]</t>
+  </si>
+  <si>
+    <t>PlcCardCm</t>
   </si>
 </sst>
 </file>
@@ -6439,7 +6442,9 @@
       <c r="Y3" s="18"/>
       <c r="Z3" s="18"/>
       <c r="AA3" s="54"/>
-      <c r="AB3" s="45"/>
+      <c r="AB3" s="45" t="s">
+        <v>107</v>
+      </c>
       <c r="AC3" s="49"/>
       <c r="AD3" s="55"/>
       <c r="AE3" s="42"/>
@@ -15878,7 +15883,9 @@
       <c r="Y3" s="18"/>
       <c r="Z3" s="18"/>
       <c r="AA3" s="54"/>
-      <c r="AB3" s="45"/>
+      <c r="AB3" s="45" t="s">
+        <v>974</v>
+      </c>
       <c r="AC3" s="49"/>
       <c r="AD3" s="55"/>
       <c r="AE3" s="42"/>
@@ -20805,7 +20812,7 @@
       <c r="AF78" s="51" t="s">
         <v>188</v>
       </c>
-      <c r="AG78" s="75" t="s">
+      <c r="AH78" s="75" t="s">
         <v>188</v>
       </c>
     </row>
@@ -20880,7 +20887,7 @@
       <c r="AF79" s="51" t="s">
         <v>194</v>
       </c>
-      <c r="AG79" s="75" t="s">
+      <c r="AH79" s="75" t="s">
         <v>188</v>
       </c>
     </row>
